--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488299_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488299_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.071899999999999</v>
+        <v>8.9975</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9877</v>
+        <v>5.0857</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0842</v>
+        <v>3.9118</v>
       </c>
       <c r="G2" t="n">
         <v>4.5988</v>
@@ -610,13 +610,13 @@
         <v>3.3352</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1587</v>
+        <v>0.0843</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.6718</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9284</v>
+        <v>0.756</v>
       </c>
       <c r="V2" t="n">
         <v>2.8321</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.49</v>
+        <v>5.3674</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1587</v>
+        <v>3.0608</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3312</v>
+        <v>2.3066</v>
       </c>
       <c r="G3" t="n">
         <v>4.7427</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2353</v>
+        <v>-0.3578</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.715</v>
+        <v>-0.8129</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4797</v>
+        <v>0.4551</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.717</v>
+        <v>3.1288</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4594</v>
+        <v>1.9698</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2576</v>
+        <v>1.1591</v>
       </c>
       <c r="G4" t="n">
         <v>3.0033</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8608</v>
+        <v>0.2726</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1567</v>
+        <v>-0.3329</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.6056</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2589</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LÓPEZ YUSTE</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5883</v>
+        <v>1.8925</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5883</v>
+        <v>3.7351</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1.8426</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5883</v>
+        <v>3.1811</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9661999999999999</v>
+        <v>-1.3869</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6221</v>
+        <v>4.568</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5883</v>
+        <v>4.2745</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.3133</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6221</v>
+        <v>3.9611</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.0934</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.7003</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.6069</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.4946</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.5394</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.0448</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.8321</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>J. LÓPEZ YUSTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5719</v>
+        <v>1.5883</v>
       </c>
       <c r="E6" t="n">
-        <v>3.833</v>
+        <v>1.5883</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2612</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1811</v>
+        <v>1.5883</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3869</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>4.568</v>
+        <v>0.6221</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2745</v>
+        <v>1.5883</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3133</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>3.9611</v>
+        <v>0.6221</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0934</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7003</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6069</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8153</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4414</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3738</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.8321</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.8321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>J. VALVERDE PIZARRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4349</v>
+        <v>1.0159</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5474</v>
+        <v>0.6973</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9824</v>
+        <v>0.3186</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9571</v>
+        <v>0.8913</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.928</v>
+        <v>0.7422</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0292</v>
+        <v>0.149</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.912</v>
+        <v>1.158</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3836</v>
+        <v>1.1165</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5284</v>
+        <v>0.0415</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9549</v>
+        <v>-0.2667</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4556</v>
+        <v>-0.3743</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4993</v>
+        <v>0.1076</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4656</v>
+        <v>-0.2841</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1057</v>
+        <v>-0.4607</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3599</v>
+        <v>0.1766</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2589</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VALVERDE PIZARRO</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.8933</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4467</v>
+        <v>-0.5474</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2201</v>
+        <v>1.4407</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8913</v>
+        <v>-0.9571</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7422</v>
+        <v>-0.928</v>
       </c>
       <c r="I9" t="n">
-        <v>0.149</v>
+        <v>-0.0292</v>
       </c>
       <c r="J9" t="n">
-        <v>1.158</v>
+        <v>-1.912</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1165</v>
+        <v>-1.3836</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0415</v>
+        <v>-0.5284</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2667</v>
+        <v>0.9549</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3743</v>
+        <v>0.4556</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1076</v>
+        <v>0.4993</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6332</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7113</v>
+        <v>0.1057</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0781</v>
+        <v>0.8182</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X9" t="n">
         <v>-1.2589</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6655</v>
+        <v>-0.2426</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3005</v>
+        <v>-0.0499</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3651</v>
+        <v>-0.1927</v>
       </c>
       <c r="G11" t="n">
         <v>0.0076</v>
@@ -1312,13 +1312,13 @@
         <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6175</v>
+        <v>-0.1946</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6019</v>
+        <v>-0.3513</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0157</v>
+        <v>0.1567</v>
       </c>
       <c r="V11" t="n">
         <v>0.315</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3503</v>
+        <v>-0.952</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7086</v>
+        <v>-1.458</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3582</v>
+        <v>0.506</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0235</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5121</v>
+        <v>-0.1138</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4924</v>
+        <v>-0.2419</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0197</v>
+        <v>0.1281</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1584</v>
+        <v>-1.6868</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0639</v>
+        <v>-2.7154</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9055</v>
+        <v>1.0286</v>
       </c>
       <c r="G13" t="n">
         <v>-1.966</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4338</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2037</v>
+        <v>-0.8552</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2301</v>
+        <v>-0.107</v>
       </c>
       <c r="V13" t="n">
         <v>0.315</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.3915</v>
+        <v>-2.7537</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.583</v>
+        <v>-2.8221</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1915</v>
+        <v>0.0684</v>
       </c>
       <c r="G14" t="n">
         <v>-1.4626</v>
@@ -1546,13 +1546,13 @@
         <v>1.8529</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0149</v>
+        <v>-0.3473</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.332</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3469</v>
+        <v>0.2238</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9439</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>18.2634</v>
+        <v>18.5369</v>
       </c>
       <c r="E15" t="n">
-        <v>9.558699999999996</v>
+        <v>9.8325</v>
       </c>
       <c r="F15" t="n">
-        <v>8.7044</v>
+        <v>8.704499999999999</v>
       </c>
       <c r="G15" t="n">
         <v>13.8922</v>
@@ -1603,13 +1603,13 @@
         <v>11.5911</v>
       </c>
       <c r="L15" t="n">
-        <v>6.2577</v>
+        <v>6.257699999999998</v>
       </c>
       <c r="M15" t="n">
         <v>-3.9568</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.529200000000001</v>
+        <v>-7.529199999999999</v>
       </c>
       <c r="O15" t="n">
         <v>3.5722</v>
@@ -1624,13 +1624,13 @@
         <v>18.5288</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7472</v>
+        <v>-1.4736</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.005</v>
+        <v>-4.7315</v>
       </c>
       <c r="U15" t="n">
-        <v>3.2578</v>
+        <v>3.257899999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-3.146100000000001</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.836</v>
+        <v>2.3257</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2558</v>
+        <v>3.7454</v>
       </c>
       <c r="F16" t="n">
         <v>-1.4198</v>
@@ -1702,10 +1702,10 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3581</v>
+        <v>0.1315</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9849</v>
+        <v>-0.4952</v>
       </c>
       <c r="U16" t="n">
         <v>0.6267</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7194</v>
+        <v>1.0138</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5048</v>
+        <v>-0.309</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2243</v>
+        <v>1.3227</v>
       </c>
       <c r="G17" t="n">
         <v>1.7881</v>
@@ -1780,13 +1780,13 @@
         <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0992</v>
+        <v>0.3936</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4377</v>
+        <v>-0.2419</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5369</v>
+        <v>0.6354</v>
       </c>
       <c r="V17" t="n">
         <v>0.3144</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.033</v>
+        <v>0.1399</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6596</v>
+        <v>0.5617</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6925</v>
+        <v>-0.4217</v>
       </c>
       <c r="G20" t="n">
         <v>1.4283</v>
@@ -2014,13 +2014,13 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0172</v>
+        <v>0.1558</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2226</v>
+        <v>-0.3205</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2054</v>
+        <v>0.4763</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2589</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0668</v>
+        <v>-0.638</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5434</v>
+        <v>-0.0338</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4766</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7645</v>
+        <v>-1.5851</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.5173</v>
+        <v>-0.0215</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2472</v>
+        <v>-1.5636</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3869</v>
+        <v>0.6072</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.4699</v>
+        <v>1.2494</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0829</v>
+        <v>-0.6422</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3775</v>
+        <v>-2.1922</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0474</v>
+        <v>-1.2708</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3301</v>
+        <v>-0.9214</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7411</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6067</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8643</v>
+        <v>-0.0469</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.8468</v>
       </c>
       <c r="V21" t="n">
-        <v>2.8321</v>
+        <v>1.2589</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8321</v>
+        <v>1.2589</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>J. PONCE GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5155</v>
+        <v>-1.1713</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06419999999999999</v>
+        <v>-1.1133</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5796</v>
+        <v>-0.0579</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5851</v>
+        <v>2.3644</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0215</v>
+        <v>0.2768</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5636</v>
+        <v>2.0875</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6072</v>
+        <v>2.4766</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2494</v>
+        <v>0.5583</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6422</v>
+        <v>1.9184</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1922</v>
+        <v>-0.1123</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2708</v>
+        <v>-0.2814</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9214</v>
+        <v>0.1692</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1117</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9224</v>
+        <v>0.9292</v>
       </c>
       <c r="T22" t="n">
-        <v>0.051</v>
+        <v>-0.1986</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8715000000000001</v>
+        <v>1.1279</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2589</v>
+        <v>-0.9444</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. PONCE GONZALEZ</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3666</v>
+        <v>-1.5134</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4071</v>
+        <v>-1.6206</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0405</v>
+        <v>0.1072</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3644</v>
+        <v>-3.7645</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2768</v>
+        <v>-3.5173</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0875</v>
+        <v>-0.2472</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4766</v>
+        <v>-2.3869</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5583</v>
+        <v>-2.4699</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9184</v>
+        <v>0.0829</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1123</v>
+        <v>-1.3775</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2814</v>
+        <v>-1.0474</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1692</v>
+        <v>-0.3301</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.5205</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7339</v>
+        <v>0.1601</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4924</v>
+        <v>-0.2129</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2264</v>
+        <v>0.373</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9444</v>
+        <v>2.8321</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3144</v>
+        <v>2.8321</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0113</v>
+        <v>-2.0863</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3237</v>
+        <v>-2.1278</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3123</v>
+        <v>0.0415</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7273</v>
@@ -2326,13 +2326,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1602</v>
+        <v>0.0852</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4924</v>
+        <v>-0.2966</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6526</v>
+        <v>0.3818</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4736</v>
+        <v>-2.1043</v>
       </c>
       <c r="E25" t="n">
         <v>1.2807</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.7543</v>
+        <v>-3.385</v>
       </c>
       <c r="G25" t="n">
         <v>-2.0719</v>
@@ -2404,13 +2404,13 @@
         <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1428</v>
+        <v>-0.7735</v>
       </c>
       <c r="T25" t="n">
         <v>-0.6056</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5372</v>
+        <v>-0.1679</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9773</v>
+        <v>-3.0752</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2329</v>
+        <v>-0.3308</v>
       </c>
       <c r="F26" t="n">
         <v>-2.7444</v>
@@ -2482,10 +2482,10 @@
         <v>0.9264</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4464</v>
+        <v>0.3485</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1057</v>
+        <v>0.0078</v>
       </c>
       <c r="U26" t="n">
         <v>0.3407</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.9292</v>
+        <v>-5.8576</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.5563</v>
+        <v>-3.1646</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.3729</v>
+        <v>-2.693</v>
       </c>
       <c r="G27" t="n">
         <v>-6.9113</v>
@@ -2560,13 +2560,13 @@
         <v>0.9264</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2768</v>
+        <v>-0.2052</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.766</v>
+        <v>-0.3743</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4892</v>
+        <v>0.1691</v>
       </c>
       <c r="V27" t="n">
         <v>1.2589</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.4116</v>
+        <v>-6.2628</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.3628</v>
+        <v>-6.5586</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0489</v>
+        <v>0.2958</v>
       </c>
       <c r="G28" t="n">
         <v>-4.132</v>
@@ -2638,13 +2638,13 @@
         <v>0.9264</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.4268</v>
+        <v>-0.2779</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.2773</v>
+        <v>-0.4731</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1495</v>
+        <v>0.1952</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2674,10 +2674,10 @@
         <v>-18.2633</v>
       </c>
       <c r="E29" t="n">
-        <v>-8.704499999999999</v>
+        <v>-8.704500000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-9.5587</v>
+        <v>-9.5589</v>
       </c>
       <c r="G29" t="n">
         <v>-13.8921</v>
@@ -2689,7 +2689,7 @@
         <v>-9.8299</v>
       </c>
       <c r="J29" t="n">
-        <v>3.956900000000001</v>
+        <v>3.9569</v>
       </c>
       <c r="K29" t="n">
         <v>7.5292</v>
@@ -2716,13 +2716,13 @@
         <v>9.264199999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>1.7471</v>
+        <v>1.7472</v>
       </c>
       <c r="T29" t="n">
-        <v>-3.2579</v>
+        <v>-3.2578</v>
       </c>
       <c r="U29" t="n">
-        <v>5.005100000000001</v>
+        <v>5.005</v>
       </c>
       <c r="V29" t="n">
         <v>3.146</v>
